--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/serotina/workspace/Windows_simulator/Server/ExcelGenerator/Excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wlsdn\workspace\Windows_simulator\GameDesign\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{406A2D2C-0BC7-5E4A-ABA6-C6A24460BEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3EBEEA3-9FCE-4258-A7B0-42703D933C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3860" yWindow="2680" windowWidth="27240" windowHeight="16180" activeTab="1" xr2:uid="{B49165A5-C54D-3A4E-88DF-6DC3AA104EFC}"/>
+    <workbookView xWindow="-26460" yWindow="6120" windowWidth="21600" windowHeight="11835" xr2:uid="{B49165A5-C54D-3A4E-88DF-6DC3AA104EFC}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemType" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
   <si>
     <t>EID</t>
     <phoneticPr fontId="0" type="noConversion"/>
@@ -147,17 +147,25 @@
   </si>
   <si>
     <t>신화, 빨강/핑크 #E6CC80</t>
+  </si>
+  <si>
+    <t>Hunting</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>사냥</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -165,7 +173,7 @@
       <b/>
       <sz val="10"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -173,7 +181,7 @@
     <font>
       <sz val="10"/>
       <color theme="0"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -181,7 +189,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -189,7 +197,14 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -258,7 +273,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -274,7 +289,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -590,10 +605,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C1ABF79-593A-9C4A-B0A1-7FAEC13FD824}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -604,7 +619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -615,7 +630,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -626,7 +641,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -637,7 +652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>2</v>
       </c>
@@ -648,7 +663,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>3</v>
       </c>
@@ -659,7 +674,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>4</v>
       </c>
@@ -670,29 +685,41 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C10" s="6" t="s">
         <v>19</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -700,14 +727,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7740DC20-C947-5342-9A28-07D623DD3A7E}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="19.1640625" customWidth="1"/>
+    <col min="4" max="4" width="19.109375" customWidth="1"/>
     <col min="10" max="10" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -718,7 +745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -729,7 +756,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -740,7 +767,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -751,7 +778,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>2</v>
       </c>
@@ -762,7 +789,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>3</v>
       </c>
@@ -773,7 +800,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>4</v>
       </c>
@@ -784,7 +811,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>5</v>
       </c>
@@ -795,7 +822,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>6</v>
       </c>
@@ -807,6 +834,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -1,218 +1,75 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wlsdn\workspace\Windows_simulator\GameDesign\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3EBEEA3-9FCE-4258-A7B0-42703D933C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-26460" yWindow="6120" windowWidth="21600" windowHeight="11835" xr2:uid="{B49165A5-C54D-3A4E-88DF-6DC3AA104EFC}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-26460" yWindow="6120" windowWidth="21600" windowHeight="11835" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ItemType" sheetId="1" r:id="rId1"/>
-    <sheet name="ItemRarity" sheetId="2" r:id="rId2"/>
+    <sheet name="ItemType" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ItemRarity" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CurrencyType" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
-  <si>
-    <t>EID</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnumID</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>Value</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>Description</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>enum</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="0" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fishing</t>
-  </si>
-  <si>
-    <t>농사</t>
-  </si>
-  <si>
-    <t>낚시</t>
-  </si>
-  <si>
-    <t>Mining</t>
-  </si>
-  <si>
-    <t>Logging</t>
-  </si>
-  <si>
-    <t>벌목</t>
-  </si>
-  <si>
-    <t>Farming</t>
-  </si>
-  <si>
-    <t>채광</t>
-  </si>
-  <si>
-    <t>Misc</t>
-  </si>
-  <si>
-    <t>기타</t>
-  </si>
-  <si>
-    <t>특수</t>
-  </si>
-  <si>
-    <t>Special</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>Common</t>
-  </si>
-  <si>
-    <t>Uncommon</t>
-  </si>
-  <si>
-    <t>Legendary</t>
-  </si>
-  <si>
-    <t>Mythic</t>
-  </si>
-  <si>
-    <t>일반, 흰색/회색 #9D9D9D</t>
-  </si>
-  <si>
-    <t>고급, 초록 #1EFF00</t>
-  </si>
-  <si>
-    <t>희귀, 파랑 #0070DD</t>
-  </si>
-  <si>
-    <t>영웅, 보라 #A335EE</t>
-  </si>
-  <si>
-    <t>전설, 주황/금색 #FF8000</t>
-  </si>
-  <si>
-    <t>신화, 빨강/핑크 #E6CC80</t>
-  </si>
-  <si>
-    <t>Hunting</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>사냥</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color theme="0"/>
       <sz val="10"/>
-      <color theme="0"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color theme="0"/>
       <sz val="10"/>
-      <color theme="0"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -225,13 +82,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.34998626667073579"/>
+        <fgColor theme="1" tint="0.3499862666707358"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <fgColor theme="2" tint="-0.09997863704336681"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -249,42 +106,101 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -604,237 +520,411 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C1ABF79-593A-9C4A-B0A1-7FAEC13FD824}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>EnumID</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>농사</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>낚시</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>채광</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>벌목</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>사냥</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
-        <v>2</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
-        <v>3</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
-        <v>4</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
-        <v>5</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
-        <v>6</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
-        <v>7</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>19</v>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>특수</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7740DC20-C947-5342-9A28-07D623DD3A7E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="19.109375" customWidth="1"/>
-    <col min="10" max="10" width="21.6640625" customWidth="1"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="19.109375" customWidth="1" min="4" max="4"/>
+    <col width="21.6640625" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>EnumID</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>일반, 흰색/회색 #9D9D9D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>고급, 초록 #1EFF00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>희귀, 파랑 #0070DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>영웅, 보라 #A335EE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>전설, 주황/금색 #FF8000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>신화, 빨강/핑크 #E6CC80</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>EnumID</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>골드</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="ItemType" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ItemRarity" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="GlobalRarity" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="CurrencyType" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>

--- a/GameDesign/Excel/Enum.xlsx
+++ b/GameDesign/Excel/Enum.xlsx
@@ -7,8 +7,9 @@
   </bookViews>
   <sheets>
     <sheet name="ItemType" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="GlobalRarity" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CurrencyType" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="IndustryType" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="GlobalRarity" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="CurrencyType" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
@@ -105,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -127,6 +128,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -695,6 +708,146 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>EID</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>EnumID</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>enum</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>농사</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>낚시</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>채광</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>벌목</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>사냥</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
@@ -849,7 +1002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
